--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-137</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>R$ 1.253.699,48</t>
-  </si>
-  <si>
-    <t>R$ 8.586,98
-R$ 8.788,11</t>
-  </si>
-  <si>
-    <t>(7.1%)
-(4.9%)</t>
-  </si>
-  <si>
-    <t>90.8</t>
-  </si>
-  <si>
-    <t>(9.8%)</t>
-  </si>
-  <si>
-    <t>17.3%</t>
-  </si>
-  <si>
-    <t>(33.1%)</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>27.2</t>
-  </si>
-  <si>
-    <t>65.7%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>19.1</t>
-  </si>
-  <si>
-    <t>72.0%</t>
-  </si>
-  <si>
-    <t>-R$ 31.569,33</t>
+167</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>R$ 1.549.607,51</t>
+  </si>
+  <si>
+    <t>R$ 8.705,66
+R$ 8.930,22</t>
+  </si>
+  <si>
+    <t>(8.0%)
+(5.6%)</t>
+  </si>
+  <si>
+    <t>91.4</t>
+  </si>
+  <si>
+    <t>(11.5%)</t>
+  </si>
+  <si>
+    <t>21.9%</t>
+  </si>
+  <si>
+    <t>(27.3%)</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>65.0%</t>
+  </si>
+  <si>
+    <t>12.2%</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>20.1</t>
+  </si>
+  <si>
+    <t>68.7%</t>
+  </si>
+  <si>
+    <t>-R$ 35.877,64</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>2.63768115942029</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>8.7328080000000003</v>
+      </c>
       <c r="AD3" s="8">
         <v>15.516197183098592</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.2848684210526313</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.626315</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.867763157894739</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>8.214044943820225</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>11.799624</v>
+      </c>
       <c r="AD5" s="8">
         <v>17.742884269662923</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>1.7625000000000002</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>9.1367419999999999</v>
+      </c>
       <c r="AD7" s="8">
         <v>16.138782692307693</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>2.9143455696202532</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>9.6567500000000006</v>
+      </c>
       <c r="AD8" s="8">
         <v>16.609493670886078</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>3.8409528571428568</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>7.6888389999999998</v>
+      </c>
       <c r="AD9" s="8">
         <v>13.784524285714285</v>
       </c>
@@ -2617,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>2.2736984374999998</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.1011319999999998</v>
+      </c>
       <c r="AD10" s="8">
         <v>15.112760937499999</v>
       </c>
@@ -2746,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>4.7955445544554456</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>10.596864</v>
+      </c>
       <c r="AD11" s="8">
         <v>16.529702970297031</v>
       </c>
@@ -2875,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>8.7870078740157478</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>13.447601000000001</v>
+      </c>
       <c r="AD12" s="8">
         <v>20.158010077519378</v>
       </c>
@@ -2987,7 +3008,7 @@
         <v>0.022164481152829849</v>
       </c>
       <c r="W13" s="6">
-        <v>0.019807318790611216</v>
+        <v>0.019697928306286874</v>
       </c>
       <c r="X13" s="8">
         <v>34.079263953488372</v>
@@ -3004,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>7.5339211764705878</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>21.421517000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>28.244186046511629</v>
       </c>
@@ -3133,7 +3156,9 @@
       <c r="AB14" s="8">
         <v>3.0597104347826085</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>9.8135890000000003</v>
+      </c>
       <c r="AD14" s="8">
         <v>16.692816379310344</v>
       </c>
@@ -3262,7 +3287,9 @@
       <c r="AB15" s="8">
         <v>3.087070909090909</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>8.8753930000000008</v>
+      </c>
       <c r="AD15" s="8">
         <v>15.773952095808383</v>
       </c>
@@ -3391,7 +3418,9 @@
       <c r="AB16" s="8">
         <v>52.171113333333331</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>68.17013</v>
+      </c>
       <c r="AD16" s="8">
         <v>76.287780000000012</v>
       </c>
@@ -3520,7 +3549,9 @@
       <c r="AB17" s="8">
         <v>3.7104944444444445</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>6.6478489999999999</v>
+      </c>
       <c r="AD17" s="8">
         <v>14.425758181818182</v>
       </c>
@@ -3649,7 +3680,9 @@
       <c r="AB18" s="8">
         <v>4.4561731481481486</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>8.6881529999999998</v>
+      </c>
       <c r="AD18" s="8">
         <v>15.415015315315316</v>
       </c>
@@ -3778,7 +3811,9 @@
       <c r="AB19" s="8">
         <v>16.16497848101266</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>21.224471000000001</v>
+      </c>
       <c r="AD19" s="8">
         <v>28.155696202531647</v>
       </c>
@@ -3907,7 +3942,9 @@
       <c r="AB20" s="8">
         <v>5.2397930232558139</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>11.809767000000001</v>
+      </c>
       <c r="AD20" s="8">
         <v>18.749095348837209</v>
       </c>
@@ -4036,7 +4073,9 @@
       <c r="AB21" s="8">
         <v>4.0311320754716986</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>8.6078609999999998</v>
+      </c>
       <c r="AD21" s="8">
         <v>14.563207547169812</v>
       </c>
@@ -4165,7 +4204,9 @@
       <c r="AB22" s="8">
         <v>5.7182291666666671</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>9.8365960000000001</v>
+      </c>
       <c r="AD22" s="8">
         <v>16.694502061855669</v>
       </c>
@@ -4294,7 +4335,9 @@
       <c r="AB23" s="8">
         <v>5.1667626436781608</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>12.526816999999999</v>
+      </c>
       <c r="AD23" s="8">
         <v>19.225046368715084</v>
       </c>
@@ -4440,7 +4483,7 @@
         <v>19538</v>
       </c>
       <c r="B25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C25" s="4">
         <v>44</v>
@@ -4476,25 +4519,59 @@
       <c t="s" r="N25" s="4">
         <v>52</v>
       </c>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
+      <c r="O25" s="5">
+        <v>15573.85</v>
+      </c>
+      <c r="P25" s="5">
+        <v>15573.85</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0.10195479635149973</v>
+      </c>
+      <c r="R25" s="7">
+        <v>139</v>
+      </c>
+      <c r="S25" s="6">
+        <v>-0.041379310344827558</v>
+      </c>
+      <c r="T25" s="6">
+        <v>0.35014420968482424</v>
+      </c>
+      <c r="U25" s="6">
+        <v>0.00083623509922080925</v>
+      </c>
+      <c r="V25" s="6">
+        <v>0.01282987186854888</v>
+      </c>
+      <c r="W25" s="6">
+        <v>0.00033392513732956205</v>
+      </c>
+      <c r="X25" s="8">
+        <v>34.822161538461536</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="Z25" s="6">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AA25" s="8">
+        <v>11.34553115942029</v>
+      </c>
+      <c r="AB25" s="8">
+        <v>11.091574725274725</v>
+      </c>
       <c r="AC25" s="8"/>
-      <c r="AD25" s="8"/>
-      <c r="AE25" s="6"/>
+      <c r="AD25" s="8">
+        <v>29.950915384615385</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>0.39560439560439559</v>
+      </c>
       <c r="AF25" s="9"/>
-      <c r="AG25" s="5"/>
+      <c r="AG25" s="5">
+        <v>-210.19999999999999</v>
+      </c>
       <c r="AH25" s="10">
         <v>3</v>
       </c>
@@ -4535,7 +4612,7 @@
         <v>19540</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C26" s="4">
         <v>44</v>
@@ -4571,25 +4648,61 @@
       <c t="s" r="N26" s="4">
         <v>52</v>
       </c>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="6"/>
+      <c r="O26" s="5">
+        <v>14416.870000000001</v>
+      </c>
+      <c r="P26" s="5">
+        <v>14416.870000000001</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>-0.31735880772281211</v>
+      </c>
+      <c r="R26" s="7">
+        <v>143</v>
+      </c>
+      <c r="S26" s="6">
+        <v>-0.30582524271844658</v>
+      </c>
+      <c r="T26" s="6">
+        <v>0.35549056071116686</v>
+      </c>
+      <c r="U26" s="6">
+        <v>0.027885470285852615</v>
+      </c>
+      <c r="V26" s="6">
+        <v>0.02769848795196183</v>
+      </c>
+      <c r="W26" s="6">
+        <v>0.0093956247091081489</v>
+      </c>
+      <c r="X26" s="8">
+        <v>24.600925555555552</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AA26" s="8">
+        <v>2.9880949999999999</v>
+      </c>
+      <c r="AB26" s="8">
+        <v>7.1348144444444443</v>
+      </c>
+      <c r="AC26" s="8">
+        <v>10.265184</v>
+      </c>
+      <c r="AD26" s="8">
+        <v>17.216481111111111</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="5"/>
+      <c r="AG26" s="5">
+        <v>-654.73000000000002</v>
+      </c>
       <c r="AH26" s="10">
         <v>3</v>
       </c>
@@ -4708,7 +4821,9 @@
       <c r="AB27" s="8">
         <v>10.242391304347825</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>15.144391000000001</v>
+      </c>
       <c r="AD27" s="8">
         <v>22.294557142857141</v>
       </c>
@@ -4837,7 +4952,9 @@
       <c r="AB28" s="8">
         <v>6.897297297297297</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>8.6762440000000005</v>
+      </c>
       <c r="AD28" s="8">
         <v>15.657656756756756</v>
       </c>
@@ -4966,7 +5083,9 @@
       <c r="AB29" s="8">
         <v>15.188332500000001</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>33.813729000000002</v>
+      </c>
       <c r="AD29" s="8">
         <v>42.263750000000002</v>
       </c>
@@ -5091,7 +5210,9 @@
       <c r="AB30" s="8">
         <v>4.9327392857142858</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>7.7517849999999999</v>
+      </c>
       <c r="AD30" s="8">
         <v>14.711310714285714</v>
       </c>
@@ -5144,7 +5265,7 @@
         <v>19551</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5180,25 +5301,59 @@
       <c t="s" r="N31" s="4">
         <v>52</v>
       </c>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="8"/>
-      <c r="AB31" s="8"/>
+      <c r="O31" s="5">
+        <v>7763.2399999999998</v>
+      </c>
+      <c r="P31" s="5">
+        <v>7763.2399999999998</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>-0.54119729443017861</v>
+      </c>
+      <c r="R31" s="7">
+        <v>62</v>
+      </c>
+      <c r="S31" s="6">
+        <v>-0.58108108108108114</v>
+      </c>
+      <c r="T31" s="6">
+        <v>1.6588723651465109</v>
+      </c>
+      <c r="U31" s="6">
+        <v>1.2776771425332722</v>
+      </c>
+      <c r="V31" s="6">
+        <v>0.023989017472086396</v>
+      </c>
+      <c r="W31" s="6">
+        <v>0.012759170140302244</v>
+      </c>
+      <c r="X31" s="8">
+        <v>32.217459523809524</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z31" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA31" s="8">
+        <v>5.7570312499999998</v>
+      </c>
+      <c r="AB31" s="8">
+        <v>11.494840476190475</v>
+      </c>
       <c r="AC31" s="8"/>
-      <c r="AD31" s="8"/>
-      <c r="AE31" s="6"/>
+      <c r="AD31" s="8">
+        <v>25.430554761904762</v>
+      </c>
+      <c r="AE31" s="6">
+        <v>0.35714285714285715</v>
+      </c>
       <c r="AF31" s="9"/>
-      <c r="AG31" s="5"/>
+      <c r="AG31" s="5">
+        <v>0</v>
+      </c>
       <c r="AH31" s="10">
         <v>5</v>
       </c>
@@ -5317,7 +5472,9 @@
       <c r="AB32" s="8">
         <v>3.748321582733813</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>6.3226699999999996</v>
+      </c>
       <c r="AD32" s="8">
         <v>12.286210791366907</v>
       </c>
@@ -5368,7 +5525,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5402,25 +5559,59 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
+      <c r="O33" s="5">
+        <v>8394.75</v>
+      </c>
+      <c r="P33" s="5">
+        <v>8394.75</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>-0.24377548786716718</v>
+      </c>
+      <c r="R33" s="7">
+        <v>74</v>
+      </c>
+      <c r="S33" s="6">
+        <v>-0.27450980392156865</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.51321935733643054</v>
+      </c>
+      <c r="U33" s="6">
+        <v>0.19813790762083444</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.059468596444206198</v>
+      </c>
+      <c r="W33" s="6">
+        <v>0.036387504094821166</v>
+      </c>
+      <c r="X33" s="8">
+        <v>17.554761904761904</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>1.5510283950617285</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>5.7587113636363636</v>
+      </c>
       <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="AD33" s="8">
+        <v>14.365152272727272</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>1</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5636,7 +5827,9 @@
       <c r="AB35" s="8">
         <v>2.6772727272727272</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>5.8208989999999998</v>
+      </c>
       <c r="AD35" s="8">
         <v>12.651515151515152</v>
       </c>
@@ -5862,7 +6055,9 @@
       <c r="AB37" s="8">
         <v>11.862601219512195</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>16.910793000000002</v>
+      </c>
       <c r="AD37" s="8">
         <v>23.855893902439025</v>
       </c>
@@ -5991,7 +6186,9 @@
       <c r="AB38" s="8">
         <v>4.3254394736842103</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>7.2204379999999997</v>
+      </c>
       <c r="AD38" s="8">
         <v>13.697082499999999</v>
       </c>
@@ -6042,7 +6239,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6078,25 +6275,59 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
+      <c r="O39" s="5">
+        <v>8899.9899999999998</v>
+      </c>
+      <c r="P39" s="5">
+        <v>8899.9899999999998</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-0.22471388425749295</v>
+      </c>
+      <c r="R39" s="7">
+        <v>99</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.2720588235294118</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.27269567718615417</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.037874334690263703</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.086187119311370006</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.056781468293784595</v>
+      </c>
+      <c r="X39" s="8">
+        <v>23.405896923076924</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.0920878787878787</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>6.6144803278688524</v>
+      </c>
       <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="AD39" s="8">
+        <v>15.901795384615385</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.86153846153846159</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>231.09999999999999</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6215,7 +6446,9 @@
       <c r="AB40" s="8">
         <v>7.3380368098159501</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>12.547874999999999</v>
+      </c>
       <c r="AD40" s="8">
         <v>19.328787878787878</v>
       </c>
@@ -6344,7 +6577,9 @@
       <c r="AB41" s="8">
         <v>18.585964473684211</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>22.847145000000001</v>
+      </c>
       <c r="AD41" s="8">
         <v>28.242307692307694</v>
       </c>
@@ -6395,7 +6630,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6431,25 +6666,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>9163.8899999999994</v>
+      </c>
+      <c r="P42" s="5">
+        <v>9163.8899999999994</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.1096510361458426</v>
+      </c>
+      <c r="R42" s="7">
+        <v>88</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.08333333333333337</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.28173802828274891</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.022204140381431904</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.039696679030411762</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.011746758199847445</v>
+      </c>
+      <c r="X42" s="8">
+        <v>32.746119178082189</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.43835616438356162</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.30136986301369861</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.2955430232558136</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>11.85891971830986</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>25.942921917808221</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.52054794520547942</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6568,7 +6837,9 @@
       <c r="AB43" s="8">
         <v>17.091194339622643</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>22.813618000000002</v>
+      </c>
       <c r="AD43" s="8">
         <v>29.432716666666668</v>
       </c>
@@ -6697,7 +6968,9 @@
       <c r="AB44" s="8">
         <v>1.9540540540540541</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>4.652971</v>
+      </c>
       <c r="AD44" s="8">
         <v>12.410389610389611</v>
       </c>
@@ -6826,7 +7099,9 @@
       <c r="AB45" s="8">
         <v>3.2520837499999997</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>7.3520709999999996</v>
+      </c>
       <c r="AD45" s="8">
         <v>13.408332926829269</v>
       </c>
@@ -6877,7 +7152,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -6911,25 +7186,59 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
+      <c r="O46" s="5">
+        <v>10958.49</v>
+      </c>
+      <c r="P46" s="5">
+        <v>10958.49</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>-0.080221448733325706</v>
+      </c>
+      <c r="R46" s="7">
+        <v>112</v>
+      </c>
+      <c r="S46" s="6">
+        <v>-0.11811023622047245</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.8297807362145696</v>
+      </c>
+      <c r="U46" s="6">
+        <v>0.48288075273144387</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.033995696487381016</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.0046820775490053835</v>
+      </c>
+      <c r="X46" s="8">
+        <v>36.046618840579711</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0.42028985507246375</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>8.2577981651376149</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>10.476960294117648</v>
+      </c>
       <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="AD46" s="8">
+        <v>27.997584057971014</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.3188405797101449</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>440.60000000000002</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -6970,7 +7279,7 @@
         <v>19597</v>
       </c>
       <c r="B47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C47" s="4">
         <v>44</v>
@@ -7006,25 +7315,59 @@
       <c t="s" r="N47" s="4">
         <v>52</v>
       </c>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="8"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="8"/>
-      <c r="AB47" s="8"/>
+      <c r="O47" s="5">
+        <v>21577.650000000001</v>
+      </c>
+      <c r="P47" s="5">
+        <v>21577.650000000001</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>0.23150894539278166</v>
+      </c>
+      <c r="R47" s="7">
+        <v>240</v>
+      </c>
+      <c r="S47" s="6">
+        <v>0.034482758620689724</v>
+      </c>
+      <c r="T47" s="6">
+        <v>0.00069858858587473608</v>
+      </c>
+      <c r="U47" s="6">
+        <v>-0.3049116145641439</v>
+      </c>
+      <c r="V47" s="6">
+        <v>0.036848869084446172</v>
+      </c>
+      <c r="W47" s="6">
+        <v>0.02483319545919041</v>
+      </c>
+      <c r="X47" s="8">
+        <v>33.497758823529409</v>
+      </c>
+      <c r="Y47" s="6">
+        <v>0.98319327731092432</v>
+      </c>
+      <c r="Z47" s="6">
+        <v>0.26050420168067229</v>
+      </c>
+      <c r="AA47" s="8">
+        <v>7.99237668161435</v>
+      </c>
+      <c r="AB47" s="8">
+        <v>10.240661206896551</v>
+      </c>
       <c r="AC47" s="8"/>
-      <c r="AD47" s="8"/>
-      <c r="AE47" s="6"/>
+      <c r="AD47" s="8">
+        <v>24.801680672268908</v>
+      </c>
+      <c r="AE47" s="6">
+        <v>0.44537815126050423</v>
+      </c>
       <c r="AF47" s="9"/>
-      <c r="AG47" s="5"/>
+      <c r="AG47" s="5">
+        <v>-556.10000000000002</v>
+      </c>
       <c r="AH47" s="10">
         <v>2</v>
       </c>
@@ -7141,7 +7484,9 @@
       <c r="AB48" s="8">
         <v>10.08</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>18.706315</v>
+      </c>
       <c r="AD48" s="8">
         <v>25.275298214285716</v>
       </c>
@@ -7268,7 +7613,9 @@
       <c r="AB49" s="8">
         <v>7.2672222222222214</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>11.460445</v>
+      </c>
       <c r="AD49" s="8">
         <v>19.280219780219781</v>
       </c>
@@ -7319,7 +7666,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7355,25 +7702,59 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
+      <c r="O50" s="5">
+        <v>8410.9300000000003</v>
+      </c>
+      <c r="P50" s="5">
+        <v>8410.9300000000003</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.11404862397787152</v>
+      </c>
+      <c r="R50" s="7">
+        <v>92</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.1785714285714286</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.25605162568229672</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.032407557784929847</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.07033954628085122</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.039578381938739235</v>
+      </c>
+      <c r="X50" s="8">
+        <v>21.121839655172415</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.5968168539325842</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>4.5163793103448278</v>
+      </c>
       <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="AD50" s="8">
+        <v>15.139081034482759</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.96551724137931039</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7587,7 +7968,9 @@
       <c r="AB52" s="8">
         <v>17.6796875</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>24.224478000000001</v>
+      </c>
       <c r="AD52" s="8">
         <v>32.184375000000003</v>
       </c>
@@ -7714,7 +8097,9 @@
       <c r="AB53" s="8">
         <v>2.7781738095238095</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>6.4567449999999997</v>
+      </c>
       <c r="AD53" s="8">
         <v>13.367459523809524</v>
       </c>
@@ -7765,7 +8150,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>44</v>
@@ -7801,25 +8186,59 @@
       <c t="s" r="N54" s="4">
         <v>52</v>
       </c>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="8"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="8"/>
+      <c r="O54" s="5">
+        <v>8281.0300000000007</v>
+      </c>
+      <c r="P54" s="5">
+        <v>8281.0300000000007</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>-0.093921714944711909</v>
+      </c>
+      <c r="R54" s="7">
+        <v>95</v>
+      </c>
+      <c r="S54" s="6">
+        <v>-0.068627450980392135</v>
+      </c>
+      <c r="T54" s="6">
+        <v>0.29452789085415698</v>
+      </c>
+      <c r="U54" s="6">
+        <v>-0.073330938301153364</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0.01628982143525624</v>
+      </c>
+      <c r="W54" s="6">
+        <v>-0.0040796253606133533</v>
+      </c>
+      <c r="X54" s="8">
+        <v>31.132107352941176</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0.44117647058823528</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AA54" s="8">
+        <v>5.7842105263157899</v>
+      </c>
+      <c r="AB54" s="8">
+        <v>8.335353030303029</v>
+      </c>
       <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
-      <c r="AE54" s="6"/>
+      <c r="AD54" s="8">
+        <v>20.794363235294117</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>0.45588235294117646</v>
+      </c>
       <c r="AF54" s="9"/>
-      <c r="AG54" s="5"/>
+      <c r="AG54" s="5">
+        <v>-127.90000000000001</v>
+      </c>
       <c r="AH54" s="10">
         <v>2</v>
       </c>
@@ -7860,7 +8279,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7896,25 +8315,59 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
+      <c r="O55" s="5">
+        <v>8719.2800000000007</v>
+      </c>
+      <c r="P55" s="5">
+        <v>8719.2800000000007</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.13779934775858749</v>
+      </c>
+      <c r="R55" s="7">
+        <v>102</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.06422018348623848</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.32079598315457236</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.085695837270967329</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.057182015028763841</v>
+      </c>
+      <c r="X55" s="8">
+        <v>39.995634523809521</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.043010752688172046</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.39285714285714285</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.7903669724770639</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>14.599634065934067</v>
+      </c>
       <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="AD55" s="8">
+        <v>24.281502197802197</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.19047619047619047</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8031,7 +8484,9 @@
       <c r="AB56" s="8">
         <v>2.7808823529411764</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>7.4370539999999998</v>
+      </c>
       <c r="AD56" s="8">
         <v>15.613395327102804</v>
       </c>
@@ -8160,7 +8615,9 @@
       <c r="AB57" s="8">
         <v>6.7146821428571437</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>15.551544</v>
+      </c>
       <c r="AD57" s="8">
         <v>22.373137647058822</v>
       </c>
@@ -8384,7 +8841,9 @@
       <c r="AB59" s="8">
         <v>6.2365934782608701</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>10.229347000000001</v>
+      </c>
       <c r="AD59" s="8">
         <v>17.178984782608694</v>
       </c>
@@ -8513,7 +8972,9 @@
       <c r="AB60" s="8">
         <v>5.0232447368421047</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>7.6010220000000004</v>
+      </c>
       <c r="AD60" s="8">
         <v>15.362392307692307</v>
       </c>
@@ -8640,7 +9101,9 @@
       <c r="AB61" s="8">
         <v>8.6962962962962962</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>11.280818999999999</v>
+      </c>
       <c r="AD61" s="8">
         <v>17.808332142857143</v>
       </c>
@@ -8689,7 +9152,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8725,25 +9188,59 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
+      <c r="O62" s="5">
+        <v>11201.030000000001</v>
+      </c>
+      <c r="P62" s="5">
+        <v>11201.030000000001</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.1783438696151628</v>
+      </c>
+      <c r="R62" s="7">
+        <v>99</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.3125</v>
+      </c>
+      <c r="T62" s="6">
+        <v>-2.2292592734775283E-05</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.28082236187207782</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.047488311342796151</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.03545995323644343</v>
+      </c>
+      <c r="X62" s="8">
+        <v>21.937420754716978</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.96226415094339623</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>2.9753468750000001</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>3.6254716981132078</v>
+      </c>
       <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="AD62" s="8">
+        <v>13.759749056603773</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.90566037735849059</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8862,7 +9359,9 @@
       <c r="AB63" s="8">
         <v>12.315961971830987</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>16.897012</v>
+      </c>
       <c r="AD63" s="8">
         <v>22.294749315068493</v>
       </c>
@@ -8989,7 +9488,9 @@
       <c r="AB64" s="8">
         <v>7.9566666666666661</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>11.958332</v>
+      </c>
       <c r="AD64" s="8">
         <v>16.663157894736845</v>
       </c>
@@ -9211,7 +9712,9 @@
       <c r="AB66" s="8">
         <v>5.8049999999999997</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>10.166764000000001</v>
+      </c>
       <c r="AD66" s="8">
         <v>16.464101923076921</v>
       </c>
@@ -9338,7 +9841,9 @@
       <c r="AB67" s="8">
         <v>16.088793103448275</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>29.725926999999999</v>
+      </c>
       <c r="AD67" s="8">
         <v>36.395115517241386</v>
       </c>
@@ -9467,7 +9972,9 @@
       <c r="AB68" s="8">
         <v>3.624478125</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>7.7369789999999998</v>
+      </c>
       <c r="AD68" s="8">
         <v>14.691665625000001</v>
       </c>
@@ -9590,7 +10097,9 @@
       <c r="AB69" s="8">
         <v>7.1734574074074073</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>10.723456000000001</v>
+      </c>
       <c r="AD69" s="8">
         <v>18.59303090909091</v>
       </c>
@@ -9719,7 +10228,9 @@
       <c r="AB70" s="8">
         <v>10.449193548387097</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>25.174713000000001</v>
+      </c>
       <c r="AD70" s="8">
         <v>32.03201111111111</v>
       </c>
@@ -9770,7 +10281,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9804,25 +10315,59 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
+      <c r="O71" s="5">
+        <v>7406.1300000000001</v>
+      </c>
+      <c r="P71" s="5">
+        <v>7406.1300000000001</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>-0.35152322821235971</v>
+      </c>
+      <c r="R71" s="7">
+        <v>85</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.32539682539682535</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.26173094450137924</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.044734105396475619</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.06625153757765527</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.028562488101073029</v>
+      </c>
+      <c r="X71" s="8">
+        <v>22.35040731707317</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>3.5427447058823534</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>2.2606846153846156</v>
+      </c>
       <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="AD71" s="8">
+        <v>13.75650487804878</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.92682926829268297</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9939,7 +10484,9 @@
       <c r="AB72" s="8">
         <v>4.44271523178808</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>10.44425</v>
+      </c>
       <c r="AD72" s="8">
         <v>17.220043790849676</v>
       </c>
@@ -10066,7 +10613,9 @@
       <c r="AB73" s="8">
         <v>5.7522233333333332</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>8.4855549999999997</v>
+      </c>
       <c r="AD73" s="8">
         <v>16.427776666666666</v>
       </c>
@@ -10208,7 +10757,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10244,25 +10793,59 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
+      <c r="O75" s="5">
+        <v>8005.54</v>
+      </c>
+      <c r="P75" s="5">
+        <v>8005.54</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.085578588105213682</v>
+      </c>
+      <c r="R75" s="7">
+        <v>77</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.22999999999999998</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.30067553219395571</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.053856204578329507</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.036168453346057852</v>
+      </c>
+      <c r="X75" s="8">
+        <v>31.768666</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.54000000000000004</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.8175560000000006</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>11.738</v>
+      </c>
       <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="AD75" s="8">
+        <v>23.832333999999999</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.44</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-338.17000000000002</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10474,7 +11057,9 @@
       <c r="AB77" s="8">
         <v>4.3122216666666668</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>8.1041659999999993</v>
+      </c>
       <c r="AD77" s="8">
         <v>15.050000000000001</v>
       </c>
@@ -10599,7 +11184,9 @@
       <c r="AB78" s="8">
         <v>3.2896130434782611</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>5.6939599999999997</v>
+      </c>
       <c r="AD78" s="8">
         <v>13.662318840579712</v>
       </c>
@@ -10728,7 +11315,9 @@
       <c r="AB79" s="8">
         <v>11.686020967741936</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>18.258600999999999</v>
+      </c>
       <c r="AD79" s="8">
         <v>25.192741935483873</v>
       </c>
@@ -10779,7 +11368,7 @@
         <v>19674</v>
       </c>
       <c r="B80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C80" s="4">
         <v>44</v>
@@ -10813,25 +11402,59 @@
       <c t="s" r="N80" s="4">
         <v>52</v>
       </c>
-      <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="6"/>
-      <c r="Z80" s="6"/>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
+      <c r="O80" s="5">
+        <v>7124.1199999999999</v>
+      </c>
+      <c r="P80" s="5">
+        <v>7124.1199999999999</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>-0.12695891727082442</v>
+      </c>
+      <c r="R80" s="7">
+        <v>75</v>
+      </c>
+      <c r="S80" s="6">
+        <v>-0.17582417582417587</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0.11117952813821215</v>
+      </c>
+      <c r="U80" s="6">
+        <v>-0.16157696669904492</v>
+      </c>
+      <c r="V80" s="6">
+        <v>0.017303400279613482</v>
+      </c>
+      <c r="W80" s="6">
+        <v>-0.013675864527829403</v>
+      </c>
+      <c r="X80" s="8">
+        <v>29.537798214285715</v>
+      </c>
+      <c r="Y80" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z80" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA80" s="8">
+        <v>5.6923611111111114</v>
+      </c>
+      <c r="AB80" s="8">
+        <v>7.8972222222222221</v>
+      </c>
       <c r="AC80" s="8"/>
-      <c r="AD80" s="8"/>
-      <c r="AE80" s="6"/>
+      <c r="AD80" s="8">
+        <v>22.953571428571429</v>
+      </c>
+      <c r="AE80" s="6">
+        <v>0.5892857142857143</v>
+      </c>
       <c r="AF80" s="9"/>
-      <c r="AG80" s="5"/>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
       <c r="AH80" s="10">
         <v>3</v>
       </c>
@@ -10948,7 +11571,9 @@
       <c r="AB81" s="8">
         <v>7.25</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>12.074999999999999</v>
+      </c>
       <c r="AD81" s="8">
         <v>19.028786363636364</v>
       </c>
@@ -11077,7 +11702,9 @@
       <c r="AB82" s="8">
         <v>7.3830188679245285</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>13.197524</v>
+      </c>
       <c r="AD82" s="8">
         <v>19.925309259259258</v>
       </c>
@@ -11299,7 +11926,9 @@
       <c r="AB84" s="8">
         <v>11.240740000000001</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>19.056365</v>
+      </c>
       <c r="AD84" s="8">
         <v>25.058681250000003</v>
       </c>
@@ -11428,7 +12057,9 @@
       <c r="AB85" s="8">
         <v>44.198715384615383</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>54.168413000000001</v>
+      </c>
       <c r="AD85" s="8">
         <v>49.149999999999999</v>
       </c>
@@ -11557,7 +12188,9 @@
       <c r="AB86" s="8">
         <v>1.9692307692307691</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>12.029913000000001</v>
+      </c>
       <c r="AD86" s="8">
         <v>20.026667499999999</v>
       </c>
@@ -11686,7 +12319,9 @@
       <c r="AB87" s="8">
         <v>2.6123340000000002</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>9.0862320000000008</v>
+      </c>
       <c r="AD87" s="8">
         <v>15.709118867924529</v>
       </c>
@@ -11813,7 +12448,9 @@
       <c r="AB88" s="8">
         <v>6.0583326923076921</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>9.6353770000000001</v>
+      </c>
       <c r="AD88" s="8">
         <v>15.853524999999999</v>
       </c>
@@ -11957,7 +12594,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -11993,25 +12630,59 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
+      <c r="O90" s="5">
+        <v>11280.309999999999</v>
+      </c>
+      <c r="P90" s="5">
+        <v>11280.309999999999</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.62340254671471484</v>
+      </c>
+      <c r="R90" s="7">
+        <v>108</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.24137931034482762</v>
+      </c>
+      <c r="T90" s="6">
+        <v>3.5130016107713353</v>
+      </c>
+      <c r="U90" s="6">
+        <v>0.1217783199220589</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.06502223786403033</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.041459055646520353</v>
+      </c>
+      <c r="X90" s="8">
+        <v>72.777255294117651</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.25882352941176473</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.84705882352941175</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>33.819182075471694</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>28.601015853658538</v>
+      </c>
       <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="AD90" s="8">
+        <v>69.78098</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.058823529411764705</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-396.73000000000002</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12130,7 +12801,9 @@
       <c r="AB91" s="8">
         <v>4.1451395833333331</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>11.654574</v>
+      </c>
       <c r="AD91" s="8">
         <v>18.132680392156864</v>
       </c>
@@ -12259,7 +12932,9 @@
       <c r="AB92" s="8">
         <v>5.7472972972972975</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>11.623174000000001</v>
+      </c>
       <c r="AD92" s="8">
         <v>19.565316216216218</v>
       </c>
@@ -12386,7 +13061,9 @@
       <c r="AB93" s="8">
         <v>4.5597014925373136</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>8.0600550000000002</v>
+      </c>
       <c r="AD93" s="8">
         <v>12.506560638297874</v>
       </c>
@@ -12513,7 +13190,9 @@
       <c r="AB94" s="8">
         <v>3.6520120689655173</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>7.5343340000000003</v>
+      </c>
       <c r="AD94" s="8">
         <v>14.669230769230769</v>
       </c>
@@ -12735,7 +13414,9 @@
       <c r="AB96" s="8">
         <v>1.3484852272727272</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>3.7857059999999998</v>
+      </c>
       <c r="AD96" s="8">
         <v>10.725946590909091</v>
       </c>
@@ -12864,7 +13545,9 @@
       <c r="AB97" s="8">
         <v>4.4878795454545459</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>19.805826</v>
+      </c>
       <c r="AD97" s="8">
         <v>24.645832692307692</v>
       </c>
@@ -12993,7 +13676,9 @@
       <c r="AB98" s="8">
         <v>9.4395825000000002</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>22.039988999999998</v>
+      </c>
       <c r="AD98" s="8">
         <v>28.615041463414634</v>
       </c>
@@ -13122,7 +13807,9 @@
       <c r="AB99" s="8">
         <v>5.1462226666666666</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>8.5489990000000002</v>
+      </c>
       <c r="AD99" s="8">
         <v>15.17820512820513</v>
       </c>
@@ -13251,7 +13938,9 @@
       <c r="AB100" s="8">
         <v>7.9303711111111106</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>15.46654</v>
+      </c>
       <c r="AD100" s="8">
         <v>24.117391304347827</v>
       </c>
@@ -13378,7 +14067,9 @@
       <c r="AB101" s="8">
         <v>9.2754638888888881</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>11.408398</v>
+      </c>
       <c r="AD101" s="8">
         <v>16.421030952380953</v>
       </c>
@@ -13602,7 +14293,9 @@
       <c r="AB103" s="8">
         <v>1.7853658536585366</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>8.3276409999999998</v>
+      </c>
       <c r="AD103" s="8">
         <v>14.277236585365854</v>
       </c>
@@ -13731,7 +14424,9 @@
       <c r="AB104" s="8">
         <v>2.8704174999999998</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>7.8670819999999999</v>
+      </c>
       <c r="AD104" s="8">
         <v>16.326667499999999</v>
       </c>
@@ -13858,7 +14553,9 @@
       <c r="AB105" s="8">
         <v>7.8795709677419348</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>10.870797</v>
+      </c>
       <c r="AD105" s="8">
         <v>16.665103125000002</v>
       </c>
@@ -13987,7 +14684,9 @@
       <c r="AB106" s="8">
         <v>0.58402916666666671</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>6.436693</v>
+      </c>
       <c r="AD106" s="8">
         <v>12.994667999999999</v>
       </c>
@@ -14116,7 +14815,9 @@
       <c r="AB107" s="8">
         <v>14.653389830508473</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>20.279095000000002</v>
+      </c>
       <c r="AD107" s="8">
         <v>27.215254237288136</v>
       </c>
@@ -14260,7 +14961,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14294,25 +14995,59 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
+      <c r="O109" s="5">
+        <v>13878.43</v>
+      </c>
+      <c r="P109" s="5">
+        <v>13878.43</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>0.16598027354908096</v>
+      </c>
+      <c r="R109" s="7">
+        <v>141</v>
+      </c>
+      <c r="S109" s="6">
+        <v>0.060150375939849621</v>
+      </c>
+      <c r="T109" s="6">
+        <v>0</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.33829835219113402</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.04871357927373629</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.030882311615939267</v>
+      </c>
+      <c r="X109" s="8">
+        <v>42.093090243902438</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.36585365853658536</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0.6097560975609756</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>11.66386923076923</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>12.349187804878049</v>
+      </c>
       <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="AD109" s="8">
+        <v>33.373578048780487</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.24390243902439024</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>-67.799999999999997</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14524,7 +15259,9 @@
       <c r="AB111" s="8">
         <v>0.77692307692307694</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.9628199999999998</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.91666923076923</v>
       </c>
@@ -14744,7 +15481,9 @@
       <c r="AB113" s="8">
         <v>2.5898550724637679</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>5.3177120000000002</v>
+      </c>
       <c r="AD113" s="8">
         <v>15.256279710144927</v>
       </c>
@@ -14873,7 +15612,9 @@
       <c r="AB114" s="8">
         <v>3.7590270833333332</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>7.2346680000000001</v>
+      </c>
       <c r="AD114" s="8">
         <v>14.753205769230769</v>
       </c>
@@ -15002,7 +15743,9 @@
       <c r="AB115" s="8">
         <v>6.2322906250000001</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>8.9609939999999995</v>
+      </c>
       <c r="AD115" s="8">
         <v>15.827777777777776</v>
       </c>
@@ -15224,7 +15967,9 @@
       <c r="AB117" s="8">
         <v>3.8697518518518517</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>10.581105000000001</v>
+      </c>
       <c r="AD117" s="8">
         <v>12.256467164179105</v>
       </c>
@@ -15275,7 +16020,7 @@
         <v>19746</v>
       </c>
       <c r="B118" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C118" s="4">
         <v>44</v>
@@ -15311,25 +16056,59 @@
       <c t="s" r="N118" s="4">
         <v>52</v>
       </c>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
-      <c r="V118" s="6"/>
-      <c r="W118" s="6"/>
-      <c r="X118" s="8"/>
-      <c r="Y118" s="6"/>
-      <c r="Z118" s="6"/>
-      <c r="AA118" s="8"/>
-      <c r="AB118" s="8"/>
+      <c r="O118" s="5">
+        <v>11887.27</v>
+      </c>
+      <c r="P118" s="5">
+        <v>11887.27</v>
+      </c>
+      <c r="Q118" s="6">
+        <v>-0.018374404819905932</v>
+      </c>
+      <c r="R118" s="7">
+        <v>142</v>
+      </c>
+      <c r="S118" s="6">
+        <v>-0.10691823899371067</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0.20085477153290873</v>
+      </c>
+      <c r="U118" s="6">
+        <v>-0.16893156292403552</v>
+      </c>
+      <c r="V118" s="6">
+        <v>0.0091691363954886189</v>
+      </c>
+      <c r="W118" s="6">
+        <v>-0.010080868021000616</v>
+      </c>
+      <c r="X118" s="8">
+        <v>27.066986538461542</v>
+      </c>
+      <c r="Y118" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Z118" s="6">
+        <v>0.13461538461538461</v>
+      </c>
+      <c r="AA118" s="8">
+        <v>7.1996093749999996</v>
+      </c>
+      <c r="AB118" s="8">
+        <v>9.7570914893617022</v>
+      </c>
       <c r="AC118" s="8"/>
-      <c r="AD118" s="8"/>
-      <c r="AE118" s="6"/>
+      <c r="AD118" s="8">
+        <v>23.559294230769233</v>
+      </c>
+      <c r="AE118" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF118" s="9"/>
-      <c r="AG118" s="5"/>
+      <c r="AG118" s="5">
+        <v>-296.39999999999998</v>
+      </c>
       <c r="AH118" s="10">
         <v>2</v>
       </c>
@@ -15448,7 +16227,9 @@
       <c r="AB119" s="8">
         <v>3.5754174999999995</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>7.4645820000000001</v>
+      </c>
       <c r="AD119" s="8">
         <v>14.4125</v>
       </c>
@@ -15575,7 +16356,9 @@
       <c r="AB120" s="8">
         <v>16.543626470588237</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>24.796077</v>
+      </c>
       <c r="AD120" s="8">
         <v>32.747549999999997</v>
       </c>
@@ -15702,7 +16485,9 @@
       <c r="AB121" s="8">
         <v>2.6005758620689656</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>8.4706880000000009</v>
+      </c>
       <c r="AD121" s="8">
         <v>16.372989655172415</v>
       </c>
@@ -15831,7 +16616,9 @@
       <c r="AB122" s="8">
         <v>3.0333339622641509</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>6.5339499999999999</v>
+      </c>
       <c r="AD122" s="8">
         <v>13.482703773584905</v>
       </c>
@@ -15960,7 +16747,9 @@
       <c r="AB123" s="8">
         <v>3.3373134328358209</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>6.6791039999999997</v>
+      </c>
       <c r="AD123" s="8">
         <v>14.627861194029851</v>
       </c>
@@ -16085,7 +16874,9 @@
       <c r="AB124" s="8">
         <v>7.1654785714285714</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>10.688808999999999</v>
+      </c>
       <c r="AD124" s="8">
         <v>18.703571428571429</v>
       </c>
@@ -16214,7 +17005,9 @@
       <c r="AB125" s="8">
         <v>5.5864578125</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>9.6318420000000007</v>
+      </c>
       <c r="AD125" s="8">
         <v>17.438204615384617</v>
       </c>
@@ -16265,7 +17058,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16301,25 +17094,59 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
+      <c r="O126" s="5">
+        <v>4316.3599999999997</v>
+      </c>
+      <c r="P126" s="5">
+        <v>4316.3599999999997</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.46749603369447479</v>
+      </c>
+      <c r="R126" s="7">
+        <v>50</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.53271028037383172</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.25189048179484569</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.093918718549889271</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.079107627723359497</v>
+      </c>
+      <c r="X126" s="8">
+        <v>39.743749999999999</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.28125</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.46875</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>5.6616660000000003</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>16.423959374999999</v>
+      </c>
       <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="AD126" s="8">
+        <v>29.963540625</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16438,7 +17265,9 @@
       <c r="AB127" s="8">
         <v>7.0583333333333336</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>14.289583</v>
+      </c>
       <c r="AD127" s="8">
         <v>24.161804166666666</v>
       </c>
@@ -16567,7 +17396,9 @@
       <c r="AB128" s="8">
         <v>15.93333125</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>24.452380000000002</v>
+      </c>
       <c r="AD128" s="8">
         <v>27.496665</v>
       </c>
@@ -16696,7 +17527,9 @@
       <c r="AB129" s="8">
         <v>14.27312857142857</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>20.903193999999999</v>
+      </c>
       <c r="AD129" s="8">
         <v>27.446999999999999</v>
       </c>
@@ -16825,7 +17658,9 @@
       <c r="AB130" s="8">
         <v>7.428260869565217</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>11.461017999999999</v>
+      </c>
       <c r="AD130" s="8">
         <v>16.055748275862069</v>
       </c>
@@ -16952,7 +17787,9 @@
       <c r="AB131" s="8">
         <v>20.513043478260869</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>27.316666000000001</v>
+      </c>
       <c r="AD131" s="8">
         <v>34.272465217391307</v>
       </c>
@@ -17081,7 +17918,9 @@
       <c r="AB132" s="8">
         <v>8.4049810344827591</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>12.349676000000001</v>
+      </c>
       <c r="AD132" s="8">
         <v>18.185333142857143</v>
       </c>
@@ -17210,7 +18049,9 @@
       <c r="AB133" s="8">
         <v>4.5933299999999999</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>8.9581470000000003</v>
+      </c>
       <c r="AD133" s="8">
         <v>10.767362499999999</v>
       </c>
@@ -17339,7 +18180,9 @@
       <c r="AB134" s="8">
         <v>6.8685166666666673</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>14.329629000000001</v>
+      </c>
       <c r="AD134" s="8">
         <v>19.913490476190475</v>
       </c>
@@ -17468,7 +18311,9 @@
       <c r="AB135" s="8">
         <v>3.7931034482758621</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>7.0971250000000001</v>
+      </c>
       <c r="AD135" s="8">
         <v>14.056896551724137</v>
       </c>
@@ -17597,7 +18442,9 @@
       <c r="AB136" s="8">
         <v>6.2492600000000005</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>10.928146999999999</v>
+      </c>
       <c r="AD136" s="8">
         <v>17.77037111111111</v>
       </c>
@@ -17724,7 +18571,9 @@
       <c r="AB137" s="8">
         <v>9.0366699999999991</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>15.706362</v>
+      </c>
       <c r="AD137" s="8">
         <v>21.612118181818182</v>
       </c>
@@ -17775,7 +18624,7 @@
         <v>19788</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>44</v>
@@ -17809,25 +18658,59 @@
       <c t="s" r="N138" s="4">
         <v>52</v>
       </c>
-      <c r="O138" s="5"/>
-      <c r="P138" s="5"/>
-      <c r="Q138" s="6"/>
-      <c r="R138" s="7"/>
-      <c r="S138" s="6"/>
-      <c r="T138" s="6"/>
-      <c r="U138" s="6"/>
-      <c r="V138" s="6"/>
-      <c r="W138" s="6"/>
-      <c r="X138" s="8"/>
-      <c r="Y138" s="6"/>
-      <c r="Z138" s="6"/>
-      <c r="AA138" s="8"/>
-      <c r="AB138" s="8"/>
+      <c r="O138" s="5">
+        <v>18383.720000000001</v>
+      </c>
+      <c r="P138" s="5">
+        <v>18383.720000000001</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0.06995807171808166</v>
+      </c>
+      <c r="R138" s="7">
+        <v>173</v>
+      </c>
+      <c r="S138" s="6">
+        <v>-0.011428571428571455</v>
+      </c>
+      <c r="T138" s="6">
+        <v>0.38019698407068864</v>
+      </c>
+      <c r="U138" s="6">
+        <v>-0.0063058564860648441</v>
+      </c>
+      <c r="V138" s="6">
+        <v>0.019909191393254463</v>
+      </c>
+      <c r="W138" s="6">
+        <v>0.0022538963822338462</v>
+      </c>
+      <c r="X138" s="8">
+        <v>29.7431375</v>
+      </c>
+      <c r="Y138" s="6">
+        <v>0.66176470588235292</v>
+      </c>
+      <c r="Z138" s="6">
+        <v>0.066176470588235295</v>
+      </c>
+      <c r="AA138" s="8">
+        <v>5.9549601190476196</v>
+      </c>
+      <c r="AB138" s="8">
+        <v>9.6210856060606069</v>
+      </c>
       <c r="AC138" s="8"/>
-      <c r="AD138" s="8"/>
-      <c r="AE138" s="6"/>
+      <c r="AD138" s="8">
+        <v>22.058455882352941</v>
+      </c>
+      <c r="AE138" s="6">
+        <v>0.46323529411764708</v>
+      </c>
       <c r="AF138" s="9"/>
-      <c r="AG138" s="5"/>
+      <c r="AG138" s="5">
+        <v>-137.59999999999999</v>
+      </c>
       <c r="AH138" s="10">
         <v>3</v>
       </c>
@@ -17946,7 +18829,9 @@
       <c r="AB139" s="8">
         <v>4.5797619047619049</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>7.5165030000000002</v>
+      </c>
       <c r="AD139" s="8">
         <v>13.81174318181818</v>
       </c>
@@ -18263,7 +19148,9 @@
       <c r="AB142" s="8">
         <v>8.8083338235294111</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>15.025482</v>
+      </c>
       <c r="AD142" s="8">
         <v>23.861764705882351</v>
       </c>
@@ -18390,7 +19277,9 @@
       <c r="AB143" s="8">
         <v>7.9016949152542368</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>12.661581</v>
+      </c>
       <c r="AD143" s="8">
         <v>20.607062711864408</v>
       </c>
@@ -18519,7 +19408,9 @@
       <c r="AB144" s="8">
         <v>1.6900848101265822</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>3.751868</v>
+      </c>
       <c r="AD144" s="8">
         <v>10.318410465116278</v>
       </c>
@@ -18648,7 +19539,9 @@
       <c r="AB145" s="8">
         <v>4.8624999999999998</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>10.563782</v>
+      </c>
       <c r="AD145" s="8">
         <v>12.2453</v>
       </c>
@@ -18777,7 +19670,9 @@
       <c r="AB146" s="8">
         <v>15.185849056603773</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>29.334923</v>
+      </c>
       <c r="AD146" s="8">
         <v>35.455660377358491</v>
       </c>
@@ -18906,7 +19801,9 @@
       <c r="AB147" s="8">
         <v>2.4153640625000001</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>12.336197</v>
+      </c>
       <c r="AD147" s="8">
         <v>19.284635937499999</v>
       </c>
@@ -19037,7 +19934,9 @@
       <c r="AB148" s="8">
         <v>13.626443999999999</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>20.998666</v>
+      </c>
       <c r="AD148" s="8">
         <v>26.601341379310345</v>
       </c>
@@ -19166,7 +20065,9 @@
       <c r="AB149" s="8">
         <v>17.70754716981132</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>25.273043999999999</v>
+      </c>
       <c r="AD149" s="8">
         <v>31.650309259259259</v>
       </c>
@@ -19293,7 +20194,9 @@
       <c r="AB150" s="8">
         <v>2.7842351351351353</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>6.4065909999999997</v>
+      </c>
       <c r="AD150" s="8">
         <v>12.840243902439026</v>
       </c>
@@ -19521,7 +20424,9 @@
       <c r="AB152" s="8">
         <v>3.0259557377049182</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>9.7653730000000003</v>
+      </c>
       <c r="AD152" s="8">
         <v>16.556877777777778</v>
       </c>
@@ -19650,7 +20555,9 @@
       <c r="AB153" s="8">
         <v>4.7055560606060611</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>7.4840900000000001</v>
+      </c>
       <c r="AD153" s="8">
         <v>15.237810447761195</v>
       </c>
@@ -19762,7 +20669,7 @@
         <v>0.0099114335334944022</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.0088810633102838349</v>
+        <v>-0.0071956088463929358</v>
       </c>
       <c r="X154" s="8">
         <v>36.430477142857143</v>
@@ -19779,7 +20686,9 @@
       <c r="AB154" s="8">
         <v>13.812255882352941</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>18.831697999999999</v>
+      </c>
       <c r="AD154" s="8">
         <v>27.380951428571429</v>
       </c>
@@ -19906,7 +20815,9 @@
       <c r="AB155" s="8">
         <v>4.2815925373134327</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>7.4651740000000002</v>
+      </c>
       <c r="AD155" s="8">
         <v>13.548010447761193</v>
       </c>
@@ -20035,7 +20946,9 @@
       <c r="AB156" s="8">
         <v>6.0565789473684211</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>27.138814</v>
+      </c>
       <c r="AD156" s="8">
         <v>34.064911842105268</v>
       </c>
@@ -20326,7 +21239,9 @@
       <c r="Z159" s="6"/>
       <c r="AA159" s="8"/>
       <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>13.651574999999999</v>
+      </c>
       <c r="AD159" s="8"/>
       <c r="AE159" s="6"/>
       <c r="AF159" s="9"/>
@@ -20445,7 +21360,9 @@
       <c r="AB160" s="8">
         <v>5.3944444444444439</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>13.150426</v>
+      </c>
       <c r="AD160" s="8">
         <v>20.076127027027027</v>
       </c>
@@ -20572,7 +21489,9 @@
       <c r="AB161" s="8">
         <v>1.6499999999999999</v>
       </c>
-      <c r="AC161" s="8"/>
+      <c r="AC161" s="8">
+        <v>2.216666</v>
+      </c>
       <c r="AD161" s="8">
         <v>3.7666666666666671</v>
       </c>
@@ -20623,7 +21542,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20659,25 +21578,59 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
+      <c r="O162" s="5">
+        <v>15620.07</v>
+      </c>
+      <c r="P162" s="5">
+        <v>15620.07</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>0.6374818116631793</v>
+      </c>
+      <c r="R162" s="7">
+        <v>153</v>
+      </c>
+      <c r="S162" s="6">
+        <v>0.33043478260869574</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.24774940829330472</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.015008697144122915</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.027000839304817455</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.020012394310652899</v>
+      </c>
+      <c r="X162" s="8">
+        <v>31.694444999999998</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>12.177699295774648</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>3.6594449999999998</v>
+      </c>
       <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="AD162" s="8">
+        <v>24.456111666666668</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.38333333333333336</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-717.70000000000005</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20718,7 +21671,7 @@
         <v>19874</v>
       </c>
       <c r="B163" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C163" s="4">
         <v>44</v>
@@ -20754,25 +21707,59 @@
       <c t="s" r="N163" s="4">
         <v>52</v>
       </c>
-      <c r="O163" s="5"/>
-      <c r="P163" s="5"/>
-      <c r="Q163" s="6"/>
-      <c r="R163" s="7"/>
-      <c r="S163" s="6"/>
-      <c r="T163" s="6"/>
-      <c r="U163" s="6"/>
-      <c r="V163" s="6"/>
-      <c r="W163" s="6"/>
-      <c r="X163" s="8"/>
-      <c r="Y163" s="6"/>
-      <c r="Z163" s="6"/>
-      <c r="AA163" s="8"/>
-      <c r="AB163" s="8"/>
+      <c r="O163" s="5">
+        <v>12119.219999999999</v>
+      </c>
+      <c r="P163" s="5">
+        <v>12119.219999999999</v>
+      </c>
+      <c r="Q163" s="6">
+        <v>-0.029937013886721098</v>
+      </c>
+      <c r="R163" s="7">
+        <v>121</v>
+      </c>
+      <c r="S163" s="6">
+        <v>-0.039682539682539653</v>
+      </c>
+      <c r="T163" s="6">
+        <v>0.29211435224379129</v>
+      </c>
+      <c r="U163" s="6">
+        <v>0.0031419596310653655</v>
+      </c>
+      <c r="V163" s="6">
+        <v>0.027568317102915865</v>
+      </c>
+      <c r="W163" s="6">
+        <v>0.01249639003170171</v>
+      </c>
+      <c r="X163" s="8">
+        <v>30.230645161290319</v>
+      </c>
+      <c r="Y163" s="6">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="Z163" s="6">
+        <v>0.13978494623655913</v>
+      </c>
+      <c r="AA163" s="8">
+        <v>5.0600577586206894</v>
+      </c>
+      <c r="AB163" s="8">
+        <v>8.8617420454545464</v>
+      </c>
       <c r="AC163" s="8"/>
-      <c r="AD163" s="8"/>
-      <c r="AE163" s="6"/>
+      <c r="AD163" s="8">
+        <v>21.35179247311828</v>
+      </c>
+      <c r="AE163" s="6">
+        <v>0.58064516129032262</v>
+      </c>
       <c r="AF163" s="9"/>
-      <c r="AG163" s="5"/>
+      <c r="AG163" s="5">
+        <v>-88.730000000000004</v>
+      </c>
       <c r="AH163" s="10">
         <v>2</v>
       </c>
@@ -20813,7 +21800,7 @@
         <v>19876</v>
       </c>
       <c r="B164" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C164" s="4">
         <v>44</v>
@@ -20849,25 +21836,59 @@
       <c t="s" r="N164" s="4">
         <v>52</v>
       </c>
-      <c r="O164" s="5"/>
-      <c r="P164" s="5"/>
-      <c r="Q164" s="6"/>
-      <c r="R164" s="7"/>
-      <c r="S164" s="6"/>
-      <c r="T164" s="6"/>
-      <c r="U164" s="6"/>
-      <c r="V164" s="6"/>
-      <c r="W164" s="6"/>
-      <c r="X164" s="8"/>
-      <c r="Y164" s="6"/>
-      <c r="Z164" s="6"/>
-      <c r="AA164" s="8"/>
-      <c r="AB164" s="8"/>
+      <c r="O164" s="5">
+        <v>11126.530000000001</v>
+      </c>
+      <c r="P164" s="5">
+        <v>11126.530000000001</v>
+      </c>
+      <c r="Q164" s="6">
+        <v>0.051987012937897426</v>
+      </c>
+      <c r="R164" s="7">
+        <v>112</v>
+      </c>
+      <c r="S164" s="6">
+        <v>-0.05084745762711862</v>
+      </c>
+      <c r="T164" s="6">
+        <v>0.21394681001174667</v>
+      </c>
+      <c r="U164" s="6">
+        <v>-0.10012505246469473</v>
+      </c>
+      <c r="V164" s="6">
+        <v>0.010493972514341848</v>
+      </c>
+      <c r="W164" s="6">
+        <v>-0.0043183723946279744</v>
+      </c>
+      <c r="X164" s="8">
+        <v>21.784920634920635</v>
+      </c>
+      <c r="Y164" s="6">
+        <v>0.43076923076923079</v>
+      </c>
+      <c r="Z164" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="8">
+        <v>5.4548672566371676</v>
+      </c>
+      <c r="AB164" s="8">
+        <v>5.3821631578947366</v>
+      </c>
       <c r="AC164" s="8"/>
-      <c r="AD164" s="8"/>
-      <c r="AE164" s="6"/>
+      <c r="AD164" s="8">
+        <v>16.557949230769228</v>
+      </c>
+      <c r="AE164" s="6">
+        <v>0.93650793650793651</v>
+      </c>
       <c r="AF164" s="9"/>
-      <c r="AG164" s="5"/>
+      <c r="AG164" s="5">
+        <v>0</v>
+      </c>
       <c r="AH164" s="10">
         <v>2</v>
       </c>
@@ -21081,7 +22102,9 @@
       <c r="AB166" s="8">
         <v>12.261905714285714</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>15.673477999999999</v>
+      </c>
       <c r="AD166" s="8">
         <v>22.123147222222222</v>
       </c>
@@ -21210,7 +22233,9 @@
       <c r="AB167" s="8">
         <v>5.7975881578947366</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>9.0348290000000002</v>
+      </c>
       <c r="AD167" s="8">
         <v>14.797708750000002</v>
       </c>
@@ -21339,7 +22364,9 @@
       <c r="AB168" s="8">
         <v>4.6290787234042554</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>9.0697030000000005</v>
+      </c>
       <c r="AD168" s="8">
         <v>15.889931249999998</v>
       </c>
@@ -21468,7 +22495,9 @@
       <c r="AB169" s="8">
         <v>2.812798214285714</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>8.2286940000000008</v>
+      </c>
       <c r="AD169" s="8">
         <v>14.463333846153846</v>
       </c>
@@ -21597,7 +22626,9 @@
       <c r="AB170" s="8">
         <v>4.6871985507246379</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>10.116425</v>
+      </c>
       <c r="AD170" s="8">
         <v>17.047343478260867</v>
       </c>
@@ -21726,7 +22757,9 @@
       <c r="AB171" s="8">
         <v>2.4276785714285714</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>7.3153969999999999</v>
+      </c>
       <c r="AD171" s="8">
         <v>14.155847368421052</v>
       </c>
@@ -21855,7 +22888,9 @@
       <c r="AB172" s="8">
         <v>4.6813000000000002</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>7.6211370000000001</v>
+      </c>
       <c r="AD172" s="8">
         <v>14.584958536585365</v>
       </c>
@@ -21984,7 +23019,9 @@
       <c r="AB173" s="8">
         <v>19.067946153846155</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>25.050613999999999</v>
+      </c>
       <c r="AD173" s="8">
         <v>21.743478260869566</v>
       </c>
@@ -22113,7 +23150,9 @@
       <c r="AB174" s="8">
         <v>4.0508776315789472</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>10.083113000000001</v>
+      </c>
       <c r="AD174" s="8">
         <v>17.041447368421053</v>
       </c>
@@ -22164,7 +23203,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22200,25 +23239,59 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
+      <c r="O175" s="5">
+        <v>4546.8999999999996</v>
+      </c>
+      <c r="P175" s="5">
+        <v>4546.8999999999996</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>-0.18426769955561628</v>
+      </c>
+      <c r="R175" s="7">
+        <v>61</v>
+      </c>
+      <c r="S175" s="6">
+        <v>-0.17567567567567566</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.34766110976709408</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.073518155226637932</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.024615782181266359</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.0045689370780091932</v>
+      </c>
+      <c r="X175" s="8">
+        <v>26.435556666666667</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>7.6209870370370369</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>2.5161099999999998</v>
+      </c>
       <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="AD175" s="8">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-431.5</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22331,7 +23404,9 @@
       <c r="AB176" s="8">
         <v>6.8274529411764702</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>10.013560999999999</v>
+      </c>
       <c r="AD176" s="8">
         <v>17</v>
       </c>
@@ -22460,7 +23535,9 @@
       <c r="AB177" s="8">
         <v>0.9096153846153846</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>4.2679479999999996</v>
+      </c>
       <c r="AD177" s="8">
         <v>10.887037037037036</v>
       </c>
@@ -22589,7 +23666,9 @@
       <c r="AB178" s="8">
         <v>3.9380434782608695</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>9.9172940000000001</v>
+      </c>
       <c r="AD178" s="8">
         <v>16.468026530612246</v>
       </c>
@@ -22716,7 +23795,9 @@
       <c r="AB179" s="8">
         <v>1.7276735849056604</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.6687209999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.566981132075471</v>
       </c>
@@ -22860,7 +23941,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -22896,25 +23977,59 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
+      <c r="O181" s="5">
+        <v>4901.2200000000003</v>
+      </c>
+      <c r="P181" s="5">
+        <v>4901.2200000000003</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.022154373627473856</v>
+      </c>
+      <c r="R181" s="7">
+        <v>46</v>
+      </c>
+      <c r="S181" s="6">
+        <v>-0.16363636363636369</v>
+      </c>
+      <c r="T181" s="6">
+        <v>1.5993327171602172</v>
+      </c>
+      <c r="U181" s="6">
+        <v>1.3134426734568128</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.079855729797887048</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.05452326155528623</v>
+      </c>
+      <c r="X181" s="8">
+        <v>16.634261111111112</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.5041666666666664</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>1.3518555555555556</v>
+      </c>
       <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="AD181" s="8">
+        <v>11.723335000000001</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23033,7 +24148,9 @@
       <c r="AB182" s="8">
         <v>5.9583325</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>12.742447</v>
+      </c>
       <c r="AD182" s="8">
         <v>17.555555555555557</v>
       </c>
@@ -23162,7 +24279,9 @@
       <c r="AB183" s="8">
         <v>3.5255102040816326</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>8.0546760000000006</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.5</v>
       </c>
@@ -23291,7 +24410,9 @@
       <c r="AB184" s="8">
         <v>11.850000000000001</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>18.812633999999999</v>
+      </c>
       <c r="AD184" s="8">
         <v>26.619354838709679</v>
       </c>
@@ -23513,7 +24634,9 @@
       <c r="AB186" s="8">
         <v>14.913461538461538</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>22.461675</v>
+      </c>
       <c r="AD186" s="8">
         <v>28.046428571428571</v>
       </c>
@@ -23564,7 +24687,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23600,25 +24723,59 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
+      <c r="O187" s="5">
+        <v>2938.8200000000002</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2938.8200000000002</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.21332050715692397</v>
+      </c>
+      <c r="R187" s="7">
+        <v>36</v>
+      </c>
+      <c r="S187" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.33143574631995154</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.11427137422502907</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.076102993718567311</v>
+      </c>
+      <c r="X187" s="8">
+        <v>32.419047619047618</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>9.8226861111111106</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>10.8675</v>
+      </c>
       <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="AD187" s="8">
+        <v>24.973014285714289</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-183.59999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23739,7 +24896,9 @@
       <c r="AB188" s="8">
         <v>9.2582046153846154</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>14.613846000000001</v>
+      </c>
       <c r="AD188" s="8">
         <v>21.574103076923077</v>
       </c>
@@ -23790,7 +24949,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23826,25 +24985,59 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
+      <c r="O189" s="5">
+        <v>6044.6300000000001</v>
+      </c>
+      <c r="P189" s="5">
+        <v>6044.6300000000001</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.117087964280566</v>
+      </c>
+      <c r="R189" s="7">
+        <v>82</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.17142857142857149</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.33328250033500811</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.031235890368806696</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.073435264027740324</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.045526194324549234</v>
+      </c>
+      <c r="X189" s="8">
+        <v>30.676667142857145</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.12857142857142856</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>7.1579268292682929</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>15.393988524590165</v>
+      </c>
       <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="AD189" s="8">
+        <v>26.990714285714283</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.48571428571428571</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23885,7 +25078,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -23921,25 +25114,59 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
+      <c r="O190" s="5">
+        <v>6242.6300000000001</v>
+      </c>
+      <c r="P190" s="5">
+        <v>6242.6300000000001</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.40081470226605864</v>
+      </c>
+      <c r="R190" s="7">
+        <v>66</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.34653465346534651</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.13471575281572029</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.14947856912871657</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.085593972412268543</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.062853556914313366</v>
+      </c>
+      <c r="X190" s="8">
+        <v>19.948766666666668</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.7413983870967744</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>3.0566680000000002</v>
+      </c>
       <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="AD190" s="8">
+        <v>13.351233333333333</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>0</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24058,7 +25285,9 @@
       <c r="AB191" s="8">
         <v>7.4284090909090912</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>14.147974</v>
+      </c>
       <c r="AD191" s="8">
         <v>20.64855</v>
       </c>
@@ -24185,7 +25414,9 @@
       <c r="AB192" s="8">
         <v>13.869605882352941</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>18.772504999999999</v>
+      </c>
       <c r="AD192" s="8">
         <v>23.609647368421054</v>
       </c>
@@ -24312,7 +25543,9 @@
       <c r="AB193" s="8">
         <v>7.4368421052631586</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>14.285074</v>
+      </c>
       <c r="AD193" s="8">
         <v>17.951361224489798</v>
       </c>
@@ -24443,7 +25676,9 @@
       <c r="AB194" s="8">
         <v>6.1043478260869568</v>
       </c>
-      <c r="AC194" s="8"/>
+      <c r="AC194" s="8">
+        <v>16.979012999999998</v>
+      </c>
       <c r="AD194" s="8">
         <v>23.756945833333333</v>
       </c>
@@ -24572,7 +25807,9 @@
       <c r="AB195" s="8">
         <v>4.6519372093023259</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>8.7640580000000003</v>
+      </c>
       <c r="AD195" s="8">
         <v>15.675581395348836</v>
       </c>
@@ -24701,7 +25938,9 @@
       <c r="AB196" s="8">
         <v>31.728886666666664</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>39.739303999999997</v>
+      </c>
       <c r="AD196" s="8">
         <v>44.581249999999997</v>
       </c>
@@ -24830,7 +26069,9 @@
       <c r="AB197" s="8">
         <v>6.8554848101265824</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>9.6501350000000006</v>
+      </c>
       <c r="AD197" s="8">
         <v>16.351028395061729</v>
       </c>
@@ -24959,7 +26200,9 @@
       <c r="AB198" s="8">
         <v>4.3513916666666672</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>12.954165</v>
+      </c>
       <c r="AD198" s="8">
         <v>19.890274999999999</v>
       </c>
@@ -25010,7 +26253,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25046,25 +26289,59 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
+      <c r="O199" s="5">
+        <v>5472.1999999999998</v>
+      </c>
+      <c r="P199" s="5">
+        <v>5472.1999999999998</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.37142404238137949</v>
+      </c>
+      <c r="R199" s="7">
+        <v>58</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.40206185567010311</v>
+      </c>
+      <c r="T199" s="6">
+        <v>-0.3034638171119477</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.68073072987098426</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.089852527319907893</v>
+      </c>
+      <c r="W199" s="6">
+        <v>0.065039837725229338</v>
+      </c>
+      <c r="X199" s="8">
+        <v>33.357208108108104</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>8.2080549999999999</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>7.7518027027027037</v>
+      </c>
       <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="AD199" s="8">
+        <v>23.143243243243241</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.45945945945945948</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-154.80000000000001</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -25105,7 +26382,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25141,25 +26418,59 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
+      <c r="O200" s="5">
+        <v>2721.0999999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>2721.0999999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.099545408627134124</v>
+      </c>
+      <c r="R200" s="7">
+        <v>30</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.18918918918918914</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.41505273602587195</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.084349711513726069</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.03929440299878726</v>
+      </c>
+      <c r="X200" s="8">
+        <v>28.79833</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>9.1068965517241391</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>3.2462999999999997</v>
+      </c>
       <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="AD200" s="8">
+        <v>18.684999999999999</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-245.25</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25371,7 +26682,9 @@
       <c r="AB202" s="8">
         <v>9.6096774193548384</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>15.866447000000001</v>
+      </c>
       <c r="AD202" s="8">
         <v>22.713441935483871</v>
       </c>
@@ -25593,7 +26906,9 @@
       <c r="AB204" s="8">
         <v>8.2279749999999989</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>16.389469999999999</v>
+      </c>
       <c r="AD204" s="8">
         <v>22.967817241379308</v>
       </c>
@@ -25644,7 +26959,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -25680,25 +26995,55 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>4782.3999999999996</v>
+      </c>
+      <c r="P205" s="5">
+        <v>4782.3999999999996</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>62</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
+      <c r="T205" s="6">
+        <v>0.26734689695550351</v>
+      </c>
+      <c r="U205" s="6">
+        <v>-0.095832678153228518</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.066478964536634322</v>
+      </c>
+      <c r="W205" s="6">
+        <v>0.020334769153563064</v>
+      </c>
+      <c r="X205" s="8">
+        <v>24.603203846153846</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>5.336616666666667</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>3.4180541666666664</v>
+      </c>
       <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="AD205" s="8">
+        <v>14.988461538461538</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.80769230769230771</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-320.89999999999998</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>
@@ -25739,7 +27084,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25775,25 +27120,55 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>3749.4299999999998</v>
+      </c>
+      <c r="P206" s="5">
+        <v>3749.4299999999998</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>41</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
+      <c r="T206" s="6">
+        <v>0.36497894346607351</v>
+      </c>
+      <c r="U206" s="6">
+        <v>0.041897835137607579</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.024506124930989512</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.0080742939593484876</v>
+      </c>
+      <c r="X206" s="8">
+        <v>40.653966666666669</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>10.06891891891892</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>10.518335</v>
+      </c>
       <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="AD206" s="8">
+        <v>27.18809523809524</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.19047619047619047</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -25834,7 +27209,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -25870,25 +27245,47 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>0</v>
+      </c>
+      <c r="P207" s="5">
+        <v>0</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>49</v>
+      </c>
       <c r="S207" s="6"/>
       <c r="T207" s="6"/>
       <c r="U207" s="6"/>
       <c r="V207" s="6"/>
       <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
+      <c r="X207" s="8">
+        <v>48.403621739130436</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>13.009375</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>20.873486363636363</v>
+      </c>
       <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="AD207" s="8">
+        <v>41.082608695652176</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.30434782608695654</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>0</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>
@@ -26003,7 +27400,9 @@
       <c r="AB208" s="8">
         <v>6.2606659999999996</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>19.955666000000001</v>
+      </c>
       <c r="AD208" s="8">
         <v>26.899999999999999</v>
       </c>
@@ -26312,7 +27711,9 @@
       <c r="AB211" s="8">
         <v>20.459875925925925</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>30.483512000000001</v>
+      </c>
       <c r="AD211" s="8">
         <v>36.987576363636364</v>
       </c>
@@ -26787,22 +28188,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26812,10 +28215,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 1.549.607,51</t>
-  </si>
-  <si>
-    <t>R$ 8.705,66
-R$ 8.930,22</t>
+169</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 1.559.267,00</t>
+  </si>
+  <si>
+    <t>R$ 8.662,59
+R$ 8.881,69</t>
   </si>
   <si>
     <t>(8.0%)
-(5.6%)</t>
-  </si>
-  <si>
-    <t>91.4</t>
-  </si>
-  <si>
-    <t>(11.5%)</t>
-  </si>
-  <si>
-    <t>21.9%</t>
-  </si>
-  <si>
-    <t>(27.3%)</t>
+(5.7%)</t>
+  </si>
+  <si>
+    <t>91.0</t>
+  </si>
+  <si>
+    <t>(11.6%)</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>(27.4%)</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -947,31 +947,31 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>65.0%</t>
-  </si>
-  <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
-    <t>20.1</t>
-  </si>
-  <si>
-    <t>68.7%</t>
-  </si>
-  <si>
-    <t>-R$ 35.877,64</t>
+    <t>28.2</t>
+  </si>
+  <si>
+    <t>64.8%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>20.2</t>
+  </si>
+  <si>
+    <t>68.5%</t>
+  </si>
+  <si>
+    <t>-R$ 35.894,54</t>
   </si>
   <si>
     <t>2.94</t>
@@ -4561,7 +4561,9 @@
       <c r="AB25" s="8">
         <v>11.091574725274725</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>23.109871999999999</v>
+      </c>
       <c r="AD25" s="8">
         <v>29.950915384615385</v>
       </c>
@@ -5601,7 +5603,9 @@
       <c r="AB33" s="8">
         <v>5.7587113636363636</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>8.0735080000000004</v>
+      </c>
       <c r="AD33" s="8">
         <v>14.365152272727272</v>
       </c>
@@ -6317,7 +6321,9 @@
       <c r="AB39" s="8">
         <v>6.6144803278688524</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>8.6180149999999998</v>
+      </c>
       <c r="AD39" s="8">
         <v>15.901795384615385</v>
       </c>
@@ -6708,7 +6714,9 @@
       <c r="AB42" s="8">
         <v>11.85891971830986</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>19.443394000000001</v>
+      </c>
       <c r="AD42" s="8">
         <v>25.942921917808221</v>
       </c>
@@ -7228,7 +7236,9 @@
       <c r="AB46" s="8">
         <v>10.476960294117648</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>21.286863</v>
+      </c>
       <c r="AD46" s="8">
         <v>27.997584057971014</v>
       </c>
@@ -7357,7 +7367,9 @@
       <c r="AB47" s="8">
         <v>10.240661206896551</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>18.327774000000002</v>
+      </c>
       <c r="AD47" s="8">
         <v>24.801680672268908</v>
       </c>
@@ -7744,7 +7756,9 @@
       <c r="AB50" s="8">
         <v>4.5163793103448278</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>7.1928150000000004</v>
+      </c>
       <c r="AD50" s="8">
         <v>15.139081034482759</v>
       </c>
@@ -8228,7 +8242,9 @@
       <c r="AB54" s="8">
         <v>8.335353030303029</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>14.26458</v>
+      </c>
       <c r="AD54" s="8">
         <v>20.794363235294117</v>
       </c>
@@ -8357,7 +8373,9 @@
       <c r="AB55" s="8">
         <v>14.599634065934067</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>17.351406000000001</v>
+      </c>
       <c r="AD55" s="8">
         <v>24.281502197802197</v>
       </c>
@@ -9230,7 +9248,9 @@
       <c r="AB62" s="8">
         <v>3.6254716981132078</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>6.8106910000000003</v>
+      </c>
       <c r="AD62" s="8">
         <v>13.759749056603773</v>
       </c>
@@ -10357,7 +10377,9 @@
       <c r="AB71" s="8">
         <v>2.2606846153846156</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>6.1037720000000002</v>
+      </c>
       <c r="AD71" s="8">
         <v>13.75650487804878</v>
       </c>
@@ -10835,7 +10857,9 @@
       <c r="AB75" s="8">
         <v>11.738</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>16.909333</v>
+      </c>
       <c r="AD75" s="8">
         <v>23.832333999999999</v>
       </c>
@@ -11444,7 +11468,9 @@
       <c r="AB80" s="8">
         <v>7.8972222222222221</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>13.525584</v>
+      </c>
       <c r="AD80" s="8">
         <v>22.953571428571429</v>
       </c>
@@ -12672,7 +12698,9 @@
       <c r="AB90" s="8">
         <v>28.601015853658538</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>64.295721</v>
+      </c>
       <c r="AD90" s="8">
         <v>69.78098</v>
       </c>
@@ -14120,7 +14148,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14156,25 +14184,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>5402.1499999999996</v>
+      </c>
+      <c r="P102" s="5">
+        <v>5402.1499999999996</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.24421565417880342</v>
+      </c>
+      <c r="R102" s="7">
+        <v>57</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.25974025974025972</v>
+      </c>
+      <c r="T102" s="6">
+        <v>4.670362725951705E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.34414218413039255</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.014908508649334061</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0041875919772683097</v>
+      </c>
+      <c r="X102" s="8">
+        <v>48.066665853658542</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.70731707317073167</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>12.758333928571428</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>17.325641025641026</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>30.521169</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>35.969919512195119</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.097560975609756101</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -15037,7 +15101,9 @@
       <c r="AB109" s="8">
         <v>12.349187804878049</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>25.445526999999998</v>
+      </c>
       <c r="AD109" s="8">
         <v>33.373578048780487</v>
       </c>
@@ -16098,7 +16164,9 @@
       <c r="AB118" s="8">
         <v>9.7570914893617022</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>17.890425</v>
+      </c>
       <c r="AD118" s="8">
         <v>23.559294230769233</v>
       </c>
@@ -17136,7 +17204,9 @@
       <c r="AB126" s="8">
         <v>16.423959374999999</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>23.048957999999999</v>
+      </c>
       <c r="AD126" s="8">
         <v>29.963540625</v>
       </c>
@@ -18700,7 +18770,9 @@
       <c r="AB138" s="8">
         <v>9.6210856060606069</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>15.737876</v>
+      </c>
       <c r="AD138" s="8">
         <v>22.058455882352941</v>
       </c>
@@ -21620,7 +21692,9 @@
       <c r="AB162" s="8">
         <v>3.6594449999999998</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>16.520555000000002</v>
+      </c>
       <c r="AD162" s="8">
         <v>24.456111666666668</v>
       </c>
@@ -21749,7 +21823,9 @@
       <c r="AB163" s="8">
         <v>8.8617420454545464</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>14.162100000000001</v>
+      </c>
       <c r="AD163" s="8">
         <v>21.35179247311828</v>
       </c>
@@ -21878,7 +21954,9 @@
       <c r="AB164" s="8">
         <v>5.3821631578947366</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>10.749082</v>
+      </c>
       <c r="AD164" s="8">
         <v>16.557949230769228</v>
       </c>
@@ -23281,7 +23359,9 @@
       <c r="AB175" s="8">
         <v>2.5161099999999998</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>9.4961110000000009</v>
+      </c>
       <c r="AD175" s="8">
         <v>16.440000000000001</v>
       </c>
@@ -23846,7 +23926,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -23882,25 +23962,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>4257.3400000000001</v>
+      </c>
+      <c r="P180" s="5">
+        <v>4257.3400000000001</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.15496776549796742</v>
+      </c>
+      <c r="R180" s="7">
+        <v>44</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.32307692307692304</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.34863318410087046</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.004710335561641776</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.045255135835991486</v>
+      </c>
+      <c r="X180" s="8">
+        <v>46.480000000000004</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>10.421111111111111</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>18.61833</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>30.003333000000001</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>37.948329999999999</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-16.899999999999999</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -24019,7 +24135,9 @@
       <c r="AB181" s="8">
         <v>1.3518555555555556</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>5.6616989999999996</v>
+      </c>
       <c r="AD181" s="8">
         <v>11.723335000000001</v>
       </c>
@@ -24765,7 +24883,9 @@
       <c r="AB187" s="8">
         <v>10.8675</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>18.6675</v>
+      </c>
       <c r="AD187" s="8">
         <v>24.973014285714289</v>
       </c>
@@ -25027,7 +25147,9 @@
       <c r="AB189" s="8">
         <v>15.393988524590165</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>22.459703000000001</v>
+      </c>
       <c r="AD189" s="8">
         <v>26.990714285714283</v>
       </c>
@@ -25156,7 +25278,9 @@
       <c r="AB190" s="8">
         <v>3.0566680000000002</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>6.7912330000000001</v>
+      </c>
       <c r="AD190" s="8">
         <v>13.351233333333333</v>
       </c>
@@ -26331,7 +26455,9 @@
       <c r="AB199" s="8">
         <v>7.7518027027027037</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>15.995818</v>
+      </c>
       <c r="AD199" s="8">
         <v>23.143243243243241</v>
       </c>
@@ -26460,7 +26586,9 @@
       <c r="AB200" s="8">
         <v>3.2462999999999997</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>12.179629</v>
+      </c>
       <c r="AD200" s="8">
         <v>18.684999999999999</v>
       </c>
@@ -27033,7 +27161,9 @@
       <c r="AB205" s="8">
         <v>3.4180541666666664</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>8.4269429999999996</v>
+      </c>
       <c r="AD205" s="8">
         <v>14.988461538461538</v>
       </c>
@@ -27158,7 +27288,9 @@
       <c r="AB206" s="8">
         <v>10.518335</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>20.891348000000001</v>
+      </c>
       <c r="AD206" s="8">
         <v>27.18809523809524</v>
       </c>
@@ -27275,7 +27407,9 @@
       <c r="AB207" s="8">
         <v>20.873486363636363</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>35.243048999999999</v>
+      </c>
       <c r="AD207" s="8">
         <v>41.082608695652176</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -911,46 +911,49 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-169</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.559.267,00</t>
-  </si>
-  <si>
-    <t>R$ 8.662,59
-R$ 8.881,69</t>
-  </si>
-  <si>
-    <t>(8.0%)
-(5.7%)</t>
-  </si>
-  <si>
-    <t>91.0</t>
-  </si>
-  <si>
-    <t>(11.6%)</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>(27.4%)</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+173</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.592.814,96</t>
+  </si>
+  <si>
+    <t>R$ 8.656,60
+R$ 8.870,26</t>
+  </si>
+  <si>
+    <t>(8.1%)
+(5.8%)</t>
+  </si>
+  <si>
+    <t>91.1</t>
+  </si>
+  <si>
+    <t>(11.7%)</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>(27.2%)</t>
   </si>
   <si>
     <t>2.9%</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>0.8%</t>
   </si>
   <si>
     <t>28.2</t>
   </si>
   <si>
-    <t>64.8%</t>
+    <t>64.9%</t>
   </si>
   <si>
     <t>12.4%</t>
@@ -959,10 +962,10 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>13.5</t>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>13.6</t>
   </si>
   <si>
     <t>20.2</t>
@@ -971,7 +974,7 @@
     <t>68.5%</t>
   </si>
   <si>
-    <t>-R$ 35.894,54</t>
+    <t>-R$ 36.033,34</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2213,10 +2216,10 @@
         <v>-0.22972972972972971</v>
       </c>
       <c r="T7" s="6">
-        <v>0.47510541482400043</v>
+        <v>0.4663164200233072</v>
       </c>
       <c r="U7" s="6">
-        <v>0.011870340420127891</v>
+        <v>0.0030813456194346499</v>
       </c>
       <c r="V7" s="6">
         <v>0.022500915107870674</v>
@@ -5345,7 +5348,9 @@
       <c r="AB31" s="8">
         <v>11.494840476190475</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>17.700144000000002</v>
+      </c>
       <c r="AD31" s="8">
         <v>25.430554761904762</v>
       </c>
@@ -5656,7 +5661,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5692,25 +5697,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>13650.41</v>
+      </c>
+      <c r="P34" s="5">
+        <v>13650.41</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.14165855511204006</v>
+      </c>
+      <c r="R34" s="7">
+        <v>158</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.15053763440860213</v>
+      </c>
+      <c r="T34" s="6">
+        <v>-0.027366210978278308</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.3407655887259064</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.055369655563459262</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.034449404816412107</v>
+      </c>
+      <c r="X34" s="8">
+        <v>23.419151754385965</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.64912280701754388</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.043859649122807015</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>9.688486842105263</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.8475972972972974</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>12.514117000000001</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>18.336842105263159</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5886,7 +5927,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5922,25 +5963,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>5480.9200000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>5480.9200000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.26226017385124389</v>
+      </c>
+      <c r="R36" s="7">
+        <v>58</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.27500000000000002</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.28616365500682367</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.010706250045612781</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.082336998168190748</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.039356987513045255</v>
+      </c>
+      <c r="X36" s="8">
+        <v>28.028124999999999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.065847540983607</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>8.9010638297872351</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>13.786132</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>20.465624999999999</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -10910,7 +10987,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10944,25 +11021,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>9694.0699999999997</v>
+      </c>
+      <c r="P76" s="5">
+        <v>9694.0699999999997</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.069414245903637983</v>
+      </c>
+      <c r="R76" s="7">
+        <v>107</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.22463768115942029</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.20890289630671122</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.17676380508909056</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.047847550100215908</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.031525200457599337</v>
+      </c>
+      <c r="X76" s="8">
+        <v>36.804938888888891</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.40740740740740738</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.8773584905660377</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>9.6234574074074075</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>13.915717000000001</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>22.857407407407408</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.35185185185185186</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-138.80000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -15910,7 +16023,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>19.519656999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19047,7 +19162,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19083,25 +19198,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>4722.5600000000004</v>
+      </c>
+      <c r="P141" s="5">
+        <v>4722.5600000000004</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.26888457797529175</v>
+      </c>
+      <c r="R141" s="7">
+        <v>58</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.33066694758774895</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.018670911539503995</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.10184804428106789</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.050077394464019515</v>
+      </c>
+      <c r="X141" s="8">
+        <v>18.96172962962963</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.0519230769230767</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.091974074074074</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>5.1641969999999997</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>13.117285185185185</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.96296296296296291</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28259,112 +28410,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.592.814,96</t>
-  </si>
-  <si>
-    <t>R$ 8.656,60
-R$ 8.870,26</t>
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.603.625,43</t>
+  </si>
+  <si>
+    <t>R$ 8.668,25
+R$ 8.881,41</t>
   </si>
   <si>
     <t>(8.1%)
 (5.8%)</t>
   </si>
   <si>
-    <t>91.1</t>
-  </si>
-  <si>
-    <t>(11.7%)</t>
+    <t>91.2</t>
+  </si>
+  <si>
+    <t>(11.6%)</t>
   </si>
   <si>
     <t>21.6%</t>
   </si>
   <si>
-    <t>(27.2%)</t>
+    <t>(27.0%)</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -953,10 +953,10 @@
     <t>28.2</t>
   </si>
   <si>
-    <t>64.9%</t>
-  </si>
-  <si>
-    <t>12.4%</t>
+    <t>64.6%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
   </si>
   <si>
     <t>6.1</t>
@@ -971,10 +971,10 @@
     <t>20.2</t>
   </si>
   <si>
-    <t>68.5%</t>
-  </si>
-  <si>
-    <t>-R$ 36.033,34</t>
+    <t>68.2%</t>
+  </si>
+  <si>
+    <t>-R$ 36.085,24</t>
   </si>
   <si>
     <t>2.94</t>
@@ -11077,7 +11077,7 @@
         <v>-138.80000000000001</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16553,7 +16553,7 @@
         <v>-70.700000000000003</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21412,7 +21412,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21448,27 +21448,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>10810.469999999999</v>
+      </c>
+      <c r="P159" s="5">
+        <v>10810.469999999999</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.022044209640723178</v>
+      </c>
+      <c r="R159" s="7">
+        <v>105</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.039603960396039639</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.2729862346410471</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.00061796573136968145</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.050590307359439507</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.0242843280634422</v>
+      </c>
+      <c r="X159" s="8">
+        <v>35.921212499999996</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.30681818181818182</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.28409090909090912</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>6.763461538461538</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>6.5725494117647054</v>
+      </c>
       <c r="AC159" s="8">
         <v>13.651574999999999</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>20.188068181818181</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.27272727272727271</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.603.625,43</t>
-  </si>
-  <si>
-    <t>R$ 8.668,25
-R$ 8.881,41</t>
-  </si>
-  <si>
-    <t>(8.1%)
-(5.8%)</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.613.897,93</t>
+  </si>
+  <si>
+    <t>R$ 8.676,87
+R$ 8.889,36</t>
+  </si>
+  <si>
+    <t>(8.2%)
+(5.9%)</t>
   </si>
   <si>
     <t>91.2</t>
   </si>
   <si>
-    <t>(11.6%)</t>
-  </si>
-  <si>
-    <t>21.6%</t>
-  </si>
-  <si>
-    <t>(27.0%)</t>
+    <t>(11.7%)</t>
+  </si>
+  <si>
+    <t>22.3%</t>
+  </si>
+  <si>
+    <t>(26.2%)</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -950,13 +950,13 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>28.2</t>
-  </si>
-  <si>
-    <t>64.6%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>64.7%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
   </si>
   <si>
     <t>6.1</t>
@@ -971,7 +971,7 @@
     <t>20.2</t>
   </si>
   <si>
-    <t>68.2%</t>
+    <t>68.1%</t>
   </si>
   <si>
     <t>-R$ 36.085,24</t>
@@ -4840,7 +4840,7 @@
         <v>-128.09999999999999</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12640,7 +12640,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12674,25 +12674,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10272.5</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10272.5</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.23161562305519645</v>
+      </c>
+      <c r="R89" s="7">
+        <v>90</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.24369747899159666</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.32852275492820637</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.020366609880749575</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0067671939644682409</v>
+      </c>
+      <c r="X89" s="8">
+        <v>38.038297872340422</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.78723404255319152</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.46808510638297873</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>10.24945054945055</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>10.408139534883722</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>27.457446808510639</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.36170212765957449</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14222,7 +14256,7 @@
         <v>-193.69999999999999</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -20131,10 +20165,10 @@
         <v>-0.19718309859154926</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>1.4485968458942959</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.28912773497322292</v>
+        <v>1.1594691109210729</v>
       </c>
       <c r="V148" s="6">
         <v>0.022594686766136848</v>
@@ -24766,7 +24800,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25737,7 +25771,7 @@
         <v>-104.7</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27048,7 +27082,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28449,7 +28483,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-10).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.613.897,93</t>
-  </si>
-  <si>
-    <t>R$ 8.676,87
-R$ 8.889,36</t>
-  </si>
-  <si>
-    <t>(8.2%)
-(5.9%)</t>
-  </si>
-  <si>
-    <t>91.2</t>
-  </si>
-  <si>
-    <t>(11.7%)</t>
-  </si>
-  <si>
-    <t>22.3%</t>
-  </si>
-  <si>
-    <t>(26.2%)</t>
+181</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.666.847,67</t>
+  </si>
+  <si>
+    <t>R$ 8.681,50
+R$ 8.887,22</t>
+  </si>
+  <si>
+    <t>(7.9%)
+(5.7%)</t>
+  </si>
+  <si>
+    <t>91.0</t>
+  </si>
+  <si>
+    <t>(11.5%)</t>
+  </si>
+  <si>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>(25.4%)</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -950,16 +950,16 @@
     <t>0.8%</t>
   </si>
   <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>64.7%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
-  </si>
-  <si>
-    <t>6.1</t>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>12.9%</t>
+  </si>
+  <si>
+    <t>6.2</t>
   </si>
   <si>
     <t>7.3</t>
@@ -971,10 +971,10 @@
     <t>20.2</t>
   </si>
   <si>
-    <t>68.1%</t>
-  </si>
-  <si>
-    <t>-R$ 36.085,24</t>
+    <t>67.9%</t>
+  </si>
+  <si>
+    <t>-R$ 36.444,04</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>14195.23</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14195.23</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.03637057879574157</v>
+      </c>
+      <c r="R6" s="7">
+        <v>136</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.26509662752910662</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.002601409064876018</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.025575647594297524</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0025312869182112585</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.414356435643562</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.4232589552238801</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.7801980198019802</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.4557749999999992</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.415511881188118</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.96039603960396036</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7886,7 +7922,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7922,25 +7958,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1457.3499999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1457.3499999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.11316724679307744</v>
+      </c>
+      <c r="R51" s="7">
+        <v>17</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33493670017497518</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.037459086698459536</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.059401653686485749</v>
+      </c>
+      <c r="X51" s="8">
+        <v>24.169042857142859</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.0235294117647058</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>13.199999999999999</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>20.616671428571429</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8813,7 +8883,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>15.675274</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20506,7 +20578,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20542,25 +20614,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>8006.25</v>
+      </c>
+      <c r="P151" s="5">
+        <v>8006.25</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.23440334381063221</v>
+      </c>
+      <c r="R151" s="7">
+        <v>84</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.23636363636363633</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.27927116939890712</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.026287612802498049</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.036785199063231855</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.015712911787665887</v>
+      </c>
+      <c r="X151" s="8">
+        <v>26.044524285714285</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.45714285714285713</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>6.2089285714285705</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.9007246376811593</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>8.9212000000000007</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>15.799761428571429</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21256,7 +21364,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21292,25 +21400,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>8290.4500000000007</v>
+      </c>
+      <c r="P157" s="5">
+        <v>8290.4500000000007</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.11136357847691136</v>
+      </c>
+      <c r="R157" s="7">
+        <v>86</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.10256410256410264</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.33741152772165561</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.020276752166649575</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.029659668654898101</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.012589425181986502</v>
+      </c>
+      <c r="X157" s="8">
+        <v>44.341549295774648</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.21126760563380281</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.46478873239436619</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>13.166084883720931</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>9.1659619718309866</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>23.334249</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>30.335915492957746</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.29577464788732394</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>-55.899999999999999</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21351,7 +21495,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21387,25 +21531,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>8659.4400000000005</v>
+      </c>
+      <c r="P158" s="5">
+        <v>8659.4400000000005</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.093066220920733467</v>
+      </c>
+      <c r="R158" s="7">
+        <v>83</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.12631578947368416</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.26600191236384801</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.0084719566161322191</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.025129685060465805</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0057600722448564795</v>
+      </c>
+      <c r="X158" s="8">
+        <v>37.625926388888885</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>9.3335365853658541</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>7.6877319444444447</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>17.234721</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>24.177777777777777</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.30555555555555558</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-134.69999999999999</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22226,7 +22406,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22262,25 +22442,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>12341.02</v>
+      </c>
+      <c r="P165" s="5">
+        <v>12341.02</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.36849202204043729</v>
+      </c>
+      <c r="R165" s="7">
+        <v>114</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.07547169811320753</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.29014574159996498</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.00097191318059609334</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.015358049820841388</v>
+      </c>
+      <c r="W165" s="6">
+        <v>0.00087302346159393626</v>
+      </c>
+      <c r="X165" s="8">
+        <v>27.332441071428573</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>7.6494097345132737</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>3.3333339285714283</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>10.124999000000001</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>16.961607142857144</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-168.19999999999999</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
